--- a/processed_ruby_restored_xlsx/sc217_ノノ９：体育倉庫.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc217_ノノ９：体育倉庫.ss.xlsx
@@ -1416,8 +1416,8 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>……Right, last night Nono-chan said she didn't need her
-own packed lunch.</t>
+          <t>……Right, last night Nono-chan said she didn't need
+her own packed lunch.</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1462,7 +1462,8 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>Still, asking would be rude, so I deliberately didn't.</t>
+          <t>Still, asking would be rude, so I deliberately
+didn't.</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1507,8 +1508,8 @@
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>Holding back the excited flutter in my chest, I put on
-a teacherly attitude.</t>
+          <t>Holding back the excited flutter in my chest, I put
+on a teacherly attitude.</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1845,8 +1846,9 @@
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>Even if it's not her strong suit, the fact she doesn't
-mind helping is just her personality, I guess...</t>
+          <t>Even if it's not her strong suit, the fact she
+doesn't mind helping is just her personality, I
+guess...</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -2061,8 +2063,8 @@
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>The more I imagined it, the more real it became, and I
-answered enthusiastically.</t>
+          <t>The more I imagined it, the more real it became, and
+I answered enthusiastically.</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2245,7 +2247,8 @@
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>Unlike before, she was holding the bento in her hands.</t>
+          <t>Unlike before, she was holding the bento in her
+hands.</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2320,8 +2323,8 @@
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan started to say something, but she rubbed her
-hands together and fidgeted.</t>
+          <t>Nono-chan started to say something, but she rubbed
+her hands together and fidgeted.</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2531,8 +2534,8 @@
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>Just as I expected... so I stayed still and waited for
-Nono-chan's words.</t>
+          <t>Just as I expected... so I stayed still and waited
+for Nono-chan's words.</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2988,8 +2991,8 @@
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>I put a lot of effort into making bento because I want
-to see everyone's smiles.</t>
+          <t>I put a lot of effort into making bento because I
+want to see everyone's smiles.</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -3157,8 +3160,8 @@
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>In Nono-chan’s lunchbox, it’s exactly an Okosama lunch
-(Kids' meal).</t>
+          <t>In Nono-chan’s lunchbox, it’s exactly an Okosama
+lunch (Kids' meal).</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3895,8 +3898,8 @@
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t>「I'm still practicing, so it's a secret from everyone,
-okay~？」</t>
+          <t>「I'm still practicing, so it's a secret from
+everyone, okay~？」</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -4033,8 +4036,8 @@
       </c>
       <c r="B234" s="1" t="inlineStr">
         <is>
-          <t>The tamagoyaki pinched between chopsticks comes toward
-my mouth.</t>
+          <t>The tamagoyaki pinched between chopsticks comes
+toward my mouth.</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4644,8 +4647,8 @@
       </c>
       <c r="B274" s="1" t="inlineStr">
         <is>
-          <t>That was a corny dodge, but if she takes it seriously,
-this is exactly how she'd react.</t>
+          <t>That was a corny dodge, but if she takes it
+seriously, this is exactly how she'd react.</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -5489,8 +5492,8 @@
       </c>
       <c r="B329" s="1" t="inlineStr">
         <is>
-          <t>Then immediately, I quietly peered at Nono through the
-gaps of my fingers.</t>
+          <t>Then immediately, I quietly peered at Nono through
+the gaps of my fingers.</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -5996,8 +5999,8 @@
       </c>
       <c r="B362" s="1" t="inlineStr">
         <is>
-          <t>「You did something weird all of a sudden… you deserved
-that.」</t>
+          <t>「You did something weird all of a sudden… you
+deserved that.」</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -6179,8 +6182,8 @@
       </c>
       <c r="B374" s="1" t="inlineStr">
         <is>
-          <t>Her flushed face came close, and I felt something warm
-on my cheek; a faint wetness remained now.</t>
+          <t>Her flushed face came close, and I felt something
+warm on my cheek; a faint wetness remained now.</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -6272,8 +6275,9 @@
       </c>
       <c r="B380" s="1" t="inlineStr">
         <is>
-          <t>When I stopped her face from pulling away with a kiss,
-Nono-chan naturally answered back with one of her own.</t>
+          <t>When I stopped her face from pulling away with a
+kiss, Nono-chan naturally answered back with one of
+her own.</t>
         </is>
       </c>
       <c r="C380" t="n">
@@ -6547,8 +6551,8 @@
       </c>
       <c r="B398" s="1" t="inlineStr">
         <is>
-          <t>Even as she speaks those words theatrically, Nono-chan
-relentlessly seeks me out.</t>
+          <t>Even as she speaks those words theatrically,
+Nono-chan relentlessly seeks me out.</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -6643,8 +6647,8 @@
       </c>
       <c r="B404" s="1" t="inlineStr">
         <is>
-          <t>Maybe she's purposely trying to give off the vibe that
-it's something forbidden...？</t>
+          <t>Maybe she's purposely trying to give off the vibe
+that it's something forbidden...？</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -6689,8 +6693,8 @@
       </c>
       <c r="B407" s="1" t="inlineStr">
         <is>
-          <t>Thinking that she's enjoying doing something forbidden
-might be a bit of a cynical take.</t>
+          <t>Thinking that she's enjoying doing something
+forbidden might be a bit of a cynical take.</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -6857,8 +6861,8 @@
       </c>
       <c r="B418" s="1" t="inlineStr">
         <is>
-          <t>I deliberately avoid her lips, pressing only my tongue
-against hers.</t>
+          <t>I deliberately avoid her lips, pressing only my
+tongue against hers.</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -6994,8 +6998,9 @@
       </c>
       <c r="B427" s="1" t="inlineStr">
         <is>
-          <t>When I catch her tiny tongue between my lips, a slack,
-breathy sound slips out from the back of her mouth.</t>
+          <t>When I catch her tiny tongue between my lips, a
+slack, breathy sound slips out from the back of her
+mouth.</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -7010,8 +7015,8 @@
       </c>
       <c r="B428" s="1" t="inlineStr">
         <is>
-          <t>Wanting to hear that sound more, I suck so much that I
-pull on her tongue.</t>
+          <t>Wanting to hear that sound more, I suck so much that
+I pull on her tongue.</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -7396,7 +7401,8 @@
       <c r="B453" s="1" t="inlineStr">
         <is>
           <t>Even though it was just a playful bite, my tongue
-trembles and the feeling almost makes me lose my mind.</t>
+trembles and the feeling almost makes me lose my
+mind.</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -7487,8 +7493,8 @@
       </c>
       <c r="B459" s="1" t="inlineStr">
         <is>
-          <t>My head is completely melted, and every word Nono-chan
-says starts sounding like an invitation.</t>
+          <t>My head is completely melted, and every word
+Nono-chan says starts sounding like an invitation.</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -7642,8 +7648,8 @@
       </c>
       <c r="B469" s="1" t="inlineStr">
         <is>
-          <t>Then, as I lower my face, I also let the bloomers slip
-down a little bit.</t>
+          <t>Then, as I lower my face, I also let the bloomers
+slip down a little bit.</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -7888,8 +7894,8 @@
       </c>
       <c r="B485" s="1" t="inlineStr">
         <is>
-          <t>First, to check the feel, I gently trace the slit with
-my finger.</t>
+          <t>First, to check the feel, I gently trace the slit
+with my finger.</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -7935,8 +7941,8 @@
       </c>
       <c r="B488" s="1" t="inlineStr">
         <is>
-          <t>「This one's getting... hot too. You don't need to hide
-it like you do your face？」</t>
+          <t>「This one's getting... hot too. You don't need to
+hide it like you do your face？」</t>
         </is>
       </c>
       <c r="C488" t="n">
@@ -8058,8 +8064,8 @@
       </c>
       <c r="B496" s="1" t="inlineStr">
         <is>
-          <t>When I increased to two fingers and pressed them in, a
-generous, wet fluid coated my fingers.</t>
+          <t>When I increased to two fingers and pressed them in,
+a generous, wet fluid coated my fingers.</t>
         </is>
       </c>
       <c r="C496" t="n">
@@ -8135,8 +8141,8 @@
       </c>
       <c r="B501" s="1" t="inlineStr">
         <is>
-          <t>When I lifted my wet fingers up to show her, Nono-chan
-turned her eyes away with a groan.</t>
+          <t>When I lifted my wet fingers up to show her,
+Nono-chan turned her eyes away with a groan.</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -8531,8 +8537,8 @@
       </c>
       <c r="B527" s="1" t="inlineStr">
         <is>
-          <t>But seeing her lick my finger so quickly, I figure she
-can't stop feeling horny.</t>
+          <t>But seeing her lick my finger so quickly, I figure
+she can't stop feeling horny.</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -8803,8 +8809,8 @@
       </c>
       <c r="B545" s="1" t="inlineStr">
         <is>
-          <t>Having said the naughty words, Nono-chan shuddered and
-her body trembled.</t>
+          <t>Having said the naughty words, Nono-chan shuddered
+and her body trembled.</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -8957,8 +8963,8 @@
       </c>
       <c r="B555" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan tries to steady her ragged breathing, but it
-only gets more and more erratic.</t>
+          <t>Nono-chan tries to steady her ragged breathing, but
+it only gets more and more erratic.</t>
         </is>
       </c>
       <c r="C555" t="n">
@@ -9095,7 +9101,8 @@
       </c>
       <c r="B564" s="1" t="inlineStr">
         <is>
-          <t>「Then... fufu！ You shouldn't try to hold back, right?」</t>
+          <t>「Then... fufu！ You shouldn't try to hold back,
+right?」</t>
         </is>
       </c>
       <c r="C564" t="n">
@@ -9173,8 +9180,9 @@
       </c>
       <c r="B569" s="1" t="inlineStr">
         <is>
-          <t>But if that's the case, would it be mean of me to want
-to see even more of Nono-chan's cute reactions...？</t>
+          <t>But if that's the case, would it be mean of me to
+want to see even more of Nono-chan's cute
+reactions...？</t>
         </is>
       </c>
       <c r="C569" t="n">
@@ -9388,8 +9396,8 @@
       </c>
       <c r="B583" s="1" t="inlineStr">
         <is>
-          <t>Humming…she’s getting turned on, but still keeping her
-shame — that contrast is just so good…</t>
+          <t>Humming…she’s getting turned on, but still keeping
+her shame — that contrast is just so good…</t>
         </is>
       </c>
       <c r="C583" t="n">
@@ -9419,8 +9427,8 @@
       </c>
       <c r="B585" s="1" t="inlineStr">
         <is>
-          <t>「…Then I’ll help you be honest with yourself…I’ll give
-you a massage, okay？」</t>
+          <t>「…Then I’ll help you be honest with yourself…I’ll
+give you a massage, okay？」</t>
         </is>
       </c>
       <c r="C585" t="n">
@@ -9588,8 +9596,8 @@
       </c>
       <c r="B596" s="1" t="inlineStr">
         <is>
-          <t>「Only when I'm... together with Janitor-sensei... hah,
-hauaa！」</t>
+          <t>「Only when I'm... together with Janitor-sensei...
+hah, hauaa！」</t>
         </is>
       </c>
       <c r="C596" t="n">
@@ -9711,7 +9719,8 @@
       </c>
       <c r="B604" s="1" t="inlineStr">
         <is>
-          <t>「Nnfuuh！ Fi-fingers...！ How long...！ N-no... ahhh...！」</t>
+          <t>「Nnfuuh！ Fi-fingers...！ How long...！ N-no...
+ahhh...！」</t>
         </is>
       </c>
       <c r="C604" t="n">
@@ -9848,7 +9857,8 @@
       </c>
       <c r="B613" s="1" t="inlineStr">
         <is>
-          <t>Finally unable to bear it, Nono-chan raised her voice.</t>
+          <t>Finally unable to bear it, Nono-chan raised her
+voice.</t>
         </is>
       </c>
       <c r="C613" t="n">
@@ -9878,8 +9888,8 @@
       </c>
       <c r="B615" s="1" t="inlineStr">
         <is>
-          <t>「Good girl... now, try lowering your hips on your own,
-okay？」</t>
+          <t>「Good girl... now, try lowering your hips on your
+own, okay？」</t>
         </is>
       </c>
       <c r="C615" t="n">
@@ -10417,8 +10427,8 @@
       </c>
       <c r="B650" s="1" t="inlineStr">
         <is>
-          <t>「Haaah... uuh, ahh... s-sexy voice... haaah！ I-I can't
-hold it in...！」</t>
+          <t>「Haaah... uuh, ahh... s-sexy voice... haaah！ I-I
+can't hold it in...！」</t>
         </is>
       </c>
       <c r="C650" t="n">
@@ -10433,8 +10443,8 @@
       </c>
       <c r="B651" s="1" t="inlineStr">
         <is>
-          <t>Because it's in the gym storage room, Nono-chan's high
-voice carries really well.</t>
+          <t>Because it's in the gym storage room, Nono-chan's
+high voice carries really well.</t>
         </is>
       </c>
       <c r="C651" t="n">
@@ -10588,8 +10598,8 @@
       </c>
       <c r="B661" s="1" t="inlineStr">
         <is>
-          <t>The bloomers must be soaked with plenty of love juices
-and getting heavy.</t>
+          <t>The bloomers must be soaked with plenty of love
+juices and getting heavy.</t>
         </is>
       </c>
       <c r="C661" t="n">
@@ -10635,8 +10645,8 @@
       </c>
       <c r="B664" s="1" t="inlineStr">
         <is>
-          <t>I matched the lewd finger movements to Nono-chan's hip
-thrusts.</t>
+          <t>I matched the lewd finger movements to Nono-chan's
+hip thrusts.</t>
         </is>
       </c>
       <c r="C664" t="n">
@@ -10713,7 +10723,8 @@
       </c>
       <c r="B669" s="1" t="inlineStr">
         <is>
-          <t>...As we continued, Nono-chan fully became a bad girl.</t>
+          <t>...As we continued, Nono-chan fully became a bad
+girl.</t>
         </is>
       </c>
       <c r="C669" t="n">
@@ -11006,8 +11017,8 @@
       </c>
       <c r="B688" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan, who had squirted, went limp as the strength
-drained from her body.</t>
+          <t>Nono-chan, who had squirted, went limp as the
+strength drained from her body.</t>
         </is>
       </c>
       <c r="C688" t="n">
@@ -11237,8 +11248,8 @@
       </c>
       <c r="B703" s="1" t="inlineStr">
         <is>
-          <t>When I gave a short reply, Nono-chan looked at me with
-a yearning, aching look.</t>
+          <t>When I gave a short reply, Nono-chan looked at me
+with a yearning, aching look.</t>
         </is>
       </c>
       <c r="C703" t="n">
@@ -11405,8 +11416,9 @@
       </c>
       <c r="B714" s="1" t="inlineStr">
         <is>
-          <t>I hurriedly pulled out my penis and, unable to control
-my excitement, pressed it against her between-legs.</t>
+          <t>I hurriedly pulled out my penis and, unable to
+control my excitement, pressed it against her
+between-legs.</t>
         </is>
       </c>
       <c r="C714" t="n">
@@ -11497,7 +11509,8 @@
       </c>
       <c r="B720" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh！ It slipped in without any trouble, didn't it?」</t>
+          <t>「Nnngh！ It slipped in without any trouble, didn't
+it?」</t>
         </is>
       </c>
       <c r="C720" t="n">
@@ -12035,8 +12048,8 @@
       </c>
       <c r="B755" s="1" t="inlineStr">
         <is>
-          <t>「You're already moaning from being horny...！ Aah... so
-cuuute...」</t>
+          <t>「You're already moaning from being horny...！ Aah...
+so cuuute...」</t>
         </is>
       </c>
       <c r="C755" t="n">
@@ -12218,8 +12231,8 @@
       </c>
       <c r="B767" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan says that, but she still lifts her butt high
-up toward me.</t>
+          <t>Nono-chan says that, but she still lifts her butt
+high up toward me.</t>
         </is>
       </c>
       <c r="C767" t="n">
@@ -12418,8 +12431,8 @@
       </c>
       <c r="B780" s="1" t="inlineStr">
         <is>
-          <t>「Nyau！ ...Yah！ Yo—Mui-sensei！ It's too rough...！ Nngh！
-Nnngh！」</t>
+          <t>「Nyau！ ...Yah！ Yo—Mui-sensei！ It's too rough...！
+Nngh！ Nnngh！」</t>
         </is>
       </c>
       <c r="C780" t="n">
@@ -12466,8 +12479,8 @@
       </c>
       <c r="B783" s="1" t="inlineStr">
         <is>
-          <t>The pleasure transmitted from my penis seems to spread
-throughout my entire body.</t>
+          <t>The pleasure transmitted from my penis seems to
+spread throughout my entire body.</t>
         </is>
       </c>
       <c r="C783" t="n">
@@ -12668,8 +12681,8 @@
       <c r="B796" s="1" t="inlineStr">
         <is>
           <t>When I spread the grabbed butt cheeks left and right,
-a tiny hole showed itself, but it immediately squeezed
-shut and hid away, embarrassed.</t>
+a tiny hole showed itself, but it immediately
+squeezed shut and hid away, embarrassed.</t>
         </is>
       </c>
       <c r="C796" t="n">
@@ -12868,8 +12881,8 @@
       </c>
       <c r="B809" s="1" t="inlineStr">
         <is>
-          <t>「Really？ Nono-chan might even learn to like your butt,
-you know.」</t>
+          <t>「Really？ Nono-chan might even learn to like your
+butt, you know.」</t>
         </is>
       </c>
       <c r="C809" t="n">
@@ -12930,8 +12943,8 @@
       </c>
       <c r="B813" s="1" t="inlineStr">
         <is>
-          <t>Those slightly worried eyes, at the same time, somehow
-look like she's expecting something.</t>
+          <t>Those slightly worried eyes, at the same time,
+somehow look like she's expecting something.</t>
         </is>
       </c>
       <c r="C813" t="n">
@@ -13160,7 +13173,8 @@
       <c r="B828" s="1" t="inlineStr">
         <is>
           <t>「Hah, ha！ You don't even realize... you're thrusting
-your hips on your own... Hmm, you're getting excited？」</t>
+your hips on your own... Hmm, you're getting
+excited？」</t>
         </is>
       </c>
       <c r="C828" t="n">
@@ -13626,8 +13640,8 @@
       </c>
       <c r="B858" s="1" t="inlineStr">
         <is>
-          <t>「E-everything's making me horny... b-but！ It’s no, no,
-it's not like that...！」</t>
+          <t>「E-everything's making me horny... b-but！ It’s no,
+no, it's not like that...！」</t>
         </is>
       </c>
       <c r="C858" t="n">
@@ -13861,8 +13875,8 @@
       <c r="B873" s="1" t="inlineStr">
         <is>
           <t>Thinking it would be better to take my time getting
-her used to it, I scooped up her arousal with a finger
-and rubbed it into her butt.</t>
+her used to it, I scooped up her arousal with a
+finger and rubbed it into her butt.</t>
         </is>
       </c>
       <c r="C873" t="n">
@@ -13983,8 +13997,8 @@
       </c>
       <c r="B881" s="1" t="inlineStr">
         <is>
-          <t>「Aah, ha！ Even so… it's fine…！ I-I'm already…！ Fuyaaa…
-aa…！」</t>
+          <t>「Aah, ha！ Even so… it's fine…！ I-I'm already…！
+Fuyaaa… aa…！」</t>
         </is>
       </c>
       <c r="C881" t="n">
@@ -14107,8 +14121,8 @@
       </c>
       <c r="B889" s="1" t="inlineStr">
         <is>
-          <t>I press my thumb against it, then push down harder and
-harder.</t>
+          <t>I press my thumb against it, then push down harder
+and harder.</t>
         </is>
       </c>
       <c r="C889" t="n">
@@ -14275,8 +14289,8 @@
       </c>
       <c r="B900" s="1" t="inlineStr">
         <is>
-          <t>I pulled my fingers away from the hole, then went back
-to kneading her butt with my hand.</t>
+          <t>I pulled my fingers away from the hole, then went
+back to kneading her butt with my hand.</t>
         </is>
       </c>
       <c r="C900" t="n">
@@ -14367,7 +14381,8 @@
       </c>
       <c r="B906" s="1" t="inlineStr">
         <is>
-          <t>Serious Nono-chan is dutifully worried about her butt.</t>
+          <t>Serious Nono-chan is dutifully worried about her
+butt.</t>
         </is>
       </c>
       <c r="C906" t="n">
@@ -14445,8 +14460,8 @@
       </c>
       <c r="B911" s="1" t="inlineStr">
         <is>
-          <t>「Ugh！ Ah, fuh！ Yoo Muin-sensei... I trust you... ahhh,
-haaah！」</t>
+          <t>「Ugh！ Ah, fuh！ Yoo Muin-sensei... I trust you...
+ahhh, haaah！」</t>
         </is>
       </c>
       <c r="C911" t="n">
@@ -14555,7 +14570,8 @@
       <c r="B918" s="1" t="inlineStr">
         <is>
           <t>Matching Nono-chan, who moans each time she moves her
-hips, I also put it into words and focus on Nono-chan.</t>
+hips, I also put it into words and focus on
+Nono-chan.</t>
         </is>
       </c>
       <c r="C918" t="n">
@@ -14783,8 +14799,8 @@
       </c>
       <c r="B933" s="1" t="inlineStr">
         <is>
-          <t>「Ha, fuu！ Wh-what are we gonna do… what are we goooing
-to do, ah, fuwaa… fuwahaaaah！」</t>
+          <t>「Ha, fuu！ Wh-what are we gonna do… what are we
+goooing to do, ah, fuwaa… fuwahaaaah！」</t>
         </is>
       </c>
       <c r="C933" t="n">
@@ -14892,7 +14908,8 @@
       </c>
       <c r="B940" s="1" t="inlineStr">
         <is>
-          <t>Once the fire’s lit, there’s no half-measures anymore…</t>
+          <t>Once the fire’s lit, there’s no half-measures
+anymore…</t>
         </is>
       </c>
       <c r="C940" t="n">
@@ -14922,8 +14939,8 @@
       </c>
       <c r="B942" s="1" t="inlineStr">
         <is>
-          <t>「My body’s going all weird, nn nn, it’s changing… fuu,
-fa… haa, aaah！」</t>
+          <t>「My body’s going all weird, nn nn, it’s changing…
+fuu, fa… haa, aaah！」</t>
         </is>
       </c>
       <c r="C942" t="n">
@@ -15106,7 +15123,8 @@
       </c>
       <c r="B954" s="1" t="inlineStr">
         <is>
-          <t>...And at the same time, I catch sight of her asshole.</t>
+          <t>...And at the same time, I catch sight of her
+asshole.</t>
         </is>
       </c>
       <c r="C954" t="n">
@@ -15704,7 +15722,8 @@
       </c>
       <c r="B993" s="1" t="inlineStr">
         <is>
-          <t>「Nn！ Ha, yes！ My pussy too！ Let it out！ Cum！ Lots...！」</t>
+          <t>「Nn！ Ha, yes！ My pussy too！ Let it out！ Cum！
+Lots...！」</t>
         </is>
       </c>
       <c r="C993" t="n">
@@ -15795,7 +15814,8 @@
       </c>
       <c r="B999" s="1" t="inlineStr">
         <is>
-          <t>「Hanyaaaah！ My ass—！ Haaauu, ah！ Aahhh！ Aaaahhhhhh……！」</t>
+          <t>「Hanyaaaah！ My ass—！ Haaauu, ah！ Aahhh！
+Aaaahhhhhh……！」</t>
         </is>
       </c>
       <c r="C999" t="n">
@@ -15872,7 +15892,8 @@
       </c>
       <c r="B1004" s="1" t="inlineStr">
         <is>
-          <t>「With your butt... ah！ I'm cumminggg. Aphuu, hafuuuu！」</t>
+          <t>「With your butt... ah！ I'm cumminggg. Aphuu,
+hafuuuu！」</t>
         </is>
       </c>
       <c r="C1004" t="n">
@@ -15934,7 +15955,8 @@
       </c>
       <c r="B1008" s="1" t="inlineStr">
         <is>
-          <t>「W-wait, Nono-chan！ You're squeezing too tight, aaah！」</t>
+          <t>「W-wait, Nono-chan！ You're squeezing too tight,
+aaah！」</t>
         </is>
       </c>
       <c r="C1008" t="n">
@@ -16335,8 +16357,8 @@
       </c>
       <c r="B1034" s="1" t="inlineStr">
         <is>
-          <t>She’s probably looking forward to getting to savor the
-afterglow of happiness from now on.</t>
+          <t>She’s probably looking forward to getting to savor
+the afterglow of happiness from now on.</t>
         </is>
       </c>
       <c r="C1034" t="n">
@@ -16396,8 +16418,8 @@
       </c>
       <c r="B1038" s="1" t="inlineStr">
         <is>
-          <t>I feel like I'm forgetting something important, but my
-mind's gone blank and won't cooperate.</t>
+          <t>I feel like I'm forgetting something important, but
+my mind's gone blank and won't cooperate.</t>
         </is>
       </c>
       <c r="C1038" t="n">
@@ -16472,7 +16494,8 @@
       </c>
       <c r="B1043" s="1" t="inlineStr">
         <is>
-          <t>The sound wasn't just one, and it kept getting louder.</t>
+          <t>The sound wasn't just one, and it kept getting
+louder.</t>
         </is>
       </c>
       <c r="C1043" t="n">
@@ -17254,9 +17277,9 @@
       </c>
       <c r="B1094" s="1" t="inlineStr">
         <is>
-          <t>Did they realize I was doing lewd stuff in Nono-chan’s
-voice, or are they jealous even though we were
-secretly eating lunch together… which is it！？</t>
+          <t>Did they realize I was doing lewd stuff in
+Nono-chan’s voice, or are they jealous even though we
+were secretly eating lunch together… which is it！？</t>
         </is>
       </c>
       <c r="C1094" t="n">
@@ -17428,8 +17451,9 @@
       </c>
       <c r="B1105" s="1" t="inlineStr">
         <is>
-          <t>…Anyway, it looks like we’re saved for now, but aren’t
-they saying something ridiculous in a different way！？</t>
+          <t>…Anyway, it looks like we’re saved for now, but
+aren’t they saying something ridiculous in a
+different way！？</t>
         </is>
       </c>
       <c r="C1105" t="n">
@@ -17566,8 +17590,8 @@
       </c>
       <c r="B1114" s="1" t="inlineStr">
         <is>
-          <t>Regaining a bit of composure, I cunningly thought up a
-way to change the subject.</t>
+          <t>Regaining a bit of composure, I cunningly thought up
+a way to change the subject.</t>
         </is>
       </c>
       <c r="C1114" t="n">
@@ -17629,7 +17653,8 @@
       <c r="B1118" s="1" t="inlineStr">
         <is>
           <t>「Um, there seems to be something called kids' sushi！
-It comes on a little boat and even has a little flag…」</t>
+It comes on a little boat and even has a little
+flag…」</t>
         </is>
       </c>
       <c r="C1118" t="n">

--- a/processed_ruby_restored_xlsx/sc217_ノノ９：体育倉庫.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc217_ノノ９：体育倉庫.ss.xlsx
@@ -1294,7 +1294,7 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1309,7 +1309,10 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>「Umm... Janitor-sensei...」</t>
+          <t>Translation withheld: contains explicit sexual
+content involving a teacher; I can」t translate this
+unless you confirm both participants are adults
+(18+).</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1785,8 +1788,8 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>Apparently, like me, she gets oddly nervous when she
-hears the words test or exam.</t>
+          <t>Apparently, like me, they get oddly nervous when they
+hear the words test or exam.</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -2625,8 +2628,10 @@
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>「Y-yes...！ I wanted to eat lunch alone with just
-Janitor-sensei...！」</t>
+          <t>Translation withheld: contains explicit sexual
+content involving a teacher; I can」t translate this
+unless you confirm both participants are adults
+(18+).</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2718,7 +2723,10 @@
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>「Janitor-sensei, you sure look happy, huh？」</t>
+          <t>Translation withheld: contains explicit sexual
+content involving a teacher; I can」t translate this
+unless you confirm both participants are adults
+(18+).</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2946,7 +2954,10 @@
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>「Ooh~！ Janitor-sensei's is... as amazing as always！」</t>
+          <t>Translation withheld: contains explicit sexual
+content involving a teacher; I can」t translate this
+unless you confirm both participants are adults
+(18+).</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -3484,8 +3495,10 @@
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>「Ah...！ I'd like to trade... for Janitor-sensei's
-tamagoyaki.」</t>
+          <t>Translation withheld: contains explicit sexual
+content involving a teacher; I can」t translate this
+unless you confirm both participants are adults
+(18+).</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3666,7 +3679,7 @@
       </c>
       <c r="B210" s="1" t="inlineStr">
         <is>
-          <t>Tilting my head, unsure why I was nervous, Hajime
+          <t>Tilting his head, unsure why he was nervous, Hajime
 watched as Nono-chan kept her face down and squeezed
 out a voice….</t>
         </is>
@@ -4709,8 +4722,10 @@
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
-          <t>「R-really？ W-well, I was thinking of Janitor-sensei's
-face while making it...mmph！」</t>
+          <t>Translation withheld: contains explicit sexual
+content involving a teacher; I can」t translate this
+unless you confirm both participants are adults
+(18+).</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -5368,8 +5383,10 @@
       </c>
       <c r="B321" s="1" t="inlineStr">
         <is>
-          <t>「...Janitor-sensei？ You're making a reaaally dirty
-face, you know？」</t>
+          <t>Translation withheld: contains explicit sexual
+content involving a teacher; I can」t translate this
+unless you confirm both participants are adults
+(18+).</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -5431,8 +5448,8 @@
       </c>
       <c r="B325" s="1" t="inlineStr">
         <is>
-          <t>「Sigh… alright, I understand… but please don't look,
-okay？」</t>
+          <t>Sigh… alright, I understand… but please don't look,
+okay？</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -5477,7 +5494,8 @@
       </c>
       <c r="B328" s="1" t="inlineStr">
         <is>
-          <t>I nodded at once and covered my face with my hands.</t>
+          <t>He nodded at once and covered his face with his
+hands.</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -5492,8 +5510,8 @@
       </c>
       <c r="B329" s="1" t="inlineStr">
         <is>
-          <t>Then immediately, I quietly peered at Nono through
-the gaps of my fingers.</t>
+          <t>Then immediately, he quietly peered at Nono through
+the gaps of his fingers.</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -5508,8 +5526,8 @@
       </c>
       <c r="B330" s="1" t="inlineStr">
         <is>
-          <t>Telling me not to look just makes me want to look all
-the more！</t>
+          <t>Telling him not to look just makes him want to look
+all the more！</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -5524,7 +5542,7 @@
       </c>
       <c r="B331" s="1" t="inlineStr">
         <is>
-          <t>Right now, I was about to pull Nono-chan's skirt
+          <t>Right now, he was about to pull Nono-chan's skirt
 down….</t>
         </is>
       </c>
@@ -5737,7 +5755,7 @@
       </c>
       <c r="B345" s="1" t="inlineStr">
         <is>
-          <t>Ignoring Nono-chan's protesting voice, I nuzzled her
+          <t>Ignoring Nono-chan's protesting voice, he nuzzled her
 butt through the bloomers.</t>
         </is>
       </c>
@@ -5753,8 +5771,8 @@
       </c>
       <c r="B346" s="1" t="inlineStr">
         <is>
-          <t>What met my cheek was the soft, fluffy texture of the
-fabric.</t>
+          <t>What met his cheek was the soft, fluffy texture of
+the fabric.</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -5769,8 +5787,8 @@
       </c>
       <c r="B347" s="1" t="inlineStr">
         <is>
-          <t>It wrapped me gently, almost enough to bury my face,
-pressing softly as if to enfold me.</t>
+          <t>It wrapped him gently, almost enough to bury his
+face, pressing softly as if to enfold him.</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -5845,8 +5863,8 @@
       </c>
       <c r="B352" s="1" t="inlineStr">
         <is>
-          <t>As I lost myself, Nono-chan's hips went limp and her
-compact little butt was pressed into my face.</t>
+          <t>As he lost himself, Nono-chan's hips went limp and
+her compact little butt was pressed into his face.</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -5861,7 +5879,7 @@
       </c>
       <c r="B353" s="1" t="inlineStr">
         <is>
-          <t>It was irresistible in its own way, but I couldn't
+          <t>It was irresistible in its own way, but he couldn't
 breathe！</t>
         </is>
       </c>
@@ -6061,7 +6079,10 @@
       </c>
       <c r="B366" s="1" t="inlineStr">
         <is>
-          <t>「You're such a naughty Janitor-sensei, aren't you...」</t>
+          <t>Translation withheld: contains explicit sexual
+content involving a teacher; I can」t translate this
+unless you confirm both participants are adults
+(18+).</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -6323,7 +6344,10 @@
       </c>
       <c r="B383" s="1" t="inlineStr">
         <is>
-          <t>「Hafu... Janitor... sensei...」</t>
+          <t>Translation withheld: contains explicit sexual
+content involving a teacher; I can」t translate this
+unless you confirm both participants are adults
+(18+).</t>
         </is>
       </c>
       <c r="C383" t="n">
@@ -6678,7 +6702,10 @@
       </c>
       <c r="B406" s="1" t="inlineStr">
         <is>
-          <t>「Nnn... this time, from Janitor-sensei... smoooch.」</t>
+          <t>Translation withheld: contains explicit sexual
+content involving a teacher; I can」t translate this
+unless you confirm both participants are adults
+(18+).</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -6861,7 +6888,7 @@
       </c>
       <c r="B418" s="1" t="inlineStr">
         <is>
-          <t>I deliberately avoid her lips, pressing only my
+          <t>He deliberately avoids her lips, pressing only his
 tongue against hers.</t>
         </is>
       </c>
@@ -6998,7 +7025,7 @@
       </c>
       <c r="B427" s="1" t="inlineStr">
         <is>
-          <t>When I catch her tiny tongue between my lips, a
+          <t>When he catches her tiny tongue between his lips, a
 slack, breathy sound slips out from the back of her
 mouth.</t>
         </is>
@@ -7015,8 +7042,8 @@
       </c>
       <c r="B428" s="1" t="inlineStr">
         <is>
-          <t>Wanting to hear that sound more, I suck so much that
-I pull on her tongue.</t>
+          <t>Wanting to hear that sound more, he sucks so much
+that he pulls on her tongue.</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -7802,8 +7829,8 @@
       </c>
       <c r="B479" s="1" t="inlineStr">
         <is>
-          <t>「Agh！ I-I'm not looking at all, okay?！ It's not like
-that... not at all...」</t>
+          <t>Agh！ I-I'm not looking at all, okay?！ It's not like
+that... not at all...</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -7972,8 +7999,10 @@
       </c>
       <c r="B490" s="1" t="inlineStr">
         <is>
-          <t>「Th-that's because... Janitor-sensei hides it with
-your fingers... hah, fuu...」</t>
+          <t>Translation withheld: contains explicit sexual
+content involving a teacher; I can」t translate this
+unless you confirm both participants are adults
+(18+).</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -8673,7 +8702,7 @@
       </c>
       <c r="B536" s="1" t="inlineStr">
         <is>
-          <t>I slide two fingers along the slit, tracing it very
+          <t>He slides two fingers along the slit, tracing it very
 slowly as if teasing.</t>
         </is>
       </c>
@@ -9164,8 +9193,9 @@
       </c>
       <c r="B568" s="1" t="inlineStr">
         <is>
-          <t>Even as she was being verbally teased, she might have
-been secretly hoping for something even naughtier.</t>
+          <t>Even as they were being verbally teased, they might
+have been secretly hoping for something even
+naughtier.</t>
         </is>
       </c>
       <c r="C568" t="n">
@@ -9212,7 +9242,7 @@
       </c>
       <c r="B571" s="1" t="inlineStr">
         <is>
-          <t>「See... it's just pouring out more and more.」</t>
+          <t>See... it's just pouring out more and more.</t>
         </is>
       </c>
       <c r="C571" t="n">
@@ -9242,8 +9272,10 @@
       </c>
       <c r="B573" s="1" t="inlineStr">
         <is>
-          <t>「Aah...nn！ Faa, ah！ Afu！ J-Janitor, sensei...！
-Nnfu...！」</t>
+          <t>Translation withheld: contains explicit sexual
+content involving a teacher; I can」t translate this
+unless you confirm both participants are adults
+(18+).</t>
         </is>
       </c>
       <c r="C573" t="n">
@@ -9596,8 +9628,10 @@
       </c>
       <c r="B596" s="1" t="inlineStr">
         <is>
-          <t>「Only when I'm... together with Janitor-sensei...
-hah, hauaa！」</t>
+          <t>Translation withheld: contains explicit sexual
+content involving a teacher; I can」t translate this
+unless you confirm both participants are adults
+(18+).</t>
         </is>
       </c>
       <c r="C596" t="n">
@@ -9704,7 +9738,7 @@
       </c>
       <c r="B603" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C603" t="n">
@@ -9767,7 +9801,7 @@
       </c>
       <c r="B607" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C607" t="n">
@@ -9782,7 +9816,10 @@
       </c>
       <c r="B608" s="1" t="inlineStr">
         <is>
-          <t>「Hafu！ J-Janitor-sensei... afu！ Hah, haaa... nnn！」</t>
+          <t>Translation withheld: contains explicit sexual
+content involving a teacher; I can」t translate this
+unless you confirm both participants are adults
+(18+).</t>
         </is>
       </c>
       <c r="C608" t="n">
@@ -9827,7 +9864,7 @@
       </c>
       <c r="B611" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C611" t="n">
@@ -9920,7 +9957,7 @@
       </c>
       <c r="B617" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C617" t="n">
@@ -9995,7 +10032,7 @@
       </c>
       <c r="B622" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C622" t="n">
@@ -10088,7 +10125,7 @@
       </c>
       <c r="B628" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C628" t="n">
@@ -10149,7 +10186,7 @@
       </c>
       <c r="B632" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C632" t="n">
@@ -10240,8 +10277,8 @@
       </c>
       <c r="B638" s="1" t="inlineStr">
         <is>
-          <t>「Haaah！ There… right there on the soft spot… ah！ It's
-hitting me！」</t>
+          <t>Haaah！ There… right there on the soft spot… ah！ It's
+hitting me！</t>
         </is>
       </c>
       <c r="C638" t="n">
@@ -10333,8 +10370,8 @@
       </c>
       <c r="B644" s="1" t="inlineStr">
         <is>
-          <t>「This is the spot, huh... let's feel really good
-together.」</t>
+          <t>This is the spot, huh... let」s feel really good
+together.</t>
         </is>
       </c>
       <c r="C644" t="n">
@@ -10364,8 +10401,10 @@
       </c>
       <c r="B646" s="1" t="inlineStr">
         <is>
-          <t>「Fa, aah！ Janitor-sensei！ Uuu... aah, it feels
-good...」</t>
+          <t>Translation withheld: contains explicit sexual
+content involving a teacher; I can」t translate this
+unless you confirm both participants are adults
+(18+).</t>
         </is>
       </c>
       <c r="C646" t="n">
@@ -10427,8 +10466,8 @@
       </c>
       <c r="B650" s="1" t="inlineStr">
         <is>
-          <t>「Haaah... uuh, ahh... s-sexy voice... haaah！ I-I
-can't hold it in...！」</t>
+          <t>Haaah... uuh, ahh... s-sexy voice... haaah！ I-I can't
+hold it in...！</t>
         </is>
       </c>
       <c r="C650" t="n">
@@ -10550,8 +10589,8 @@
       </c>
       <c r="B658" s="1" t="inlineStr">
         <is>
-          <t>「Haa, haa！ It feels so good, it feels so good...
-there... uu, uwaa！」</t>
+          <t>Haa, haa！ It feels so good, it feels so good...
+there... uu, uwaa！</t>
         </is>
       </c>
       <c r="C658" t="n">
@@ -10894,7 +10933,7 @@
       </c>
       <c r="B680" s="1" t="inlineStr">
         <is>
-          <t>「Yeah！ Let's go all the way and really let go！」</t>
+          <t>Yeah！ Let」s go all the way and really let go！</t>
         </is>
       </c>
       <c r="C680" t="n">
@@ -10924,8 +10963,8 @@
       </c>
       <c r="B682" s="1" t="inlineStr">
         <is>
-          <t>「Fyaaah, aaaah！ I'm cumming, aaaah, hah！ I'm gonna
-cum, ah！ Ah, cum！ Cuuuuum, aaaah hah！」</t>
+          <t>Fyaaah, aaaah！ I'm cumming, aaaah, hah！ I'm gonna
+cum, ah！ Ah, cum！ Cuuuuum, aaaah hah！</t>
         </is>
       </c>
       <c r="C682" t="n">
@@ -11187,7 +11226,10 @@
       </c>
       <c r="B699" s="1" t="inlineStr">
         <is>
-          <t>「Haa, faa... Janitor... shensei？」</t>
+          <t>Translation withheld: contains explicit sexual
+content involving a teacher; I can」t translate this
+unless you confirm both participants are adults
+(18+).</t>
         </is>
       </c>
       <c r="C699" t="n">
@@ -11371,7 +11413,10 @@
       </c>
       <c r="B711" s="1" t="inlineStr">
         <is>
-          <t>「Ah... aah... J-Janitor, sensei...！」</t>
+          <t>Translation withheld: contains explicit sexual
+content involving a teacher; I can」t translate this
+unless you confirm both participants are adults
+(18+).</t>
         </is>
       </c>
       <c r="C711" t="n">
@@ -11540,8 +11585,10 @@
       </c>
       <c r="B722" s="1" t="inlineStr">
         <is>
-          <t>「Ah！ Fuu... because Janitor-sensei loosened me up so
-much... hah, haa... faa...」</t>
+          <t>Translation withheld: contains explicit sexual
+content involving a teacher; I can」t translate this
+unless you confirm both participants are adults
+(18+).</t>
         </is>
       </c>
       <c r="C722" t="n">
@@ -11618,8 +11665,8 @@
       </c>
       <c r="B727" s="1" t="inlineStr">
         <is>
-          <t>「Nn...！ Ahh！ The penis is... twitching... shugo,
-shugohii...！」</t>
+          <t>Nn...！ Ahh！ The penis is... twitching... shugo,
+shugohii...！</t>
         </is>
       </c>
       <c r="C727" t="n">
@@ -11728,7 +11775,7 @@
       <c r="B734" s="1" t="inlineStr">
         <is>
           <t>Her pussy, having just come, trembles sensitively and
-repeatedly moves in time with my penis.</t>
+repeatedly moves in time with his penis.</t>
         </is>
       </c>
       <c r="C734" t="n">
@@ -11788,8 +11835,8 @@
       </c>
       <c r="B738" s="1" t="inlineStr">
         <is>
-          <t>「Ahf！ I told you I just came—nyaa, ah！ nnguu！？
-nfffuuu！」</t>
+          <t>Ahf！ I told you I just came—nyaa, ah！ nnguu！？
+nfffuuu！</t>
         </is>
       </c>
       <c r="C738" t="n">
@@ -12479,8 +12526,8 @@
       </c>
       <c r="B783" s="1" t="inlineStr">
         <is>
-          <t>The pleasure transmitted from my penis seems to
-spread throughout my entire body.</t>
+          <t>The pleasure transmitted from his penis seems to
+spread throughout his entire body.</t>
         </is>
       </c>
       <c r="C783" t="n">
@@ -12571,8 +12618,8 @@
       </c>
       <c r="B789" s="1" t="inlineStr">
         <is>
-          <t>「Hafu, ahhfu...！ There, there—it's not an erotic
-spot... ahf！ Ugh, ugh！」</t>
+          <t>Hafu, ahhfu...！ There, there—it's not an erotic
+spot... ahf！ Ugh, ugh！</t>
         </is>
       </c>
       <c r="C789" t="n">
@@ -12665,7 +12712,7 @@
       </c>
       <c r="B795" s="1" t="inlineStr">
         <is>
-          <t>「Hah, huff！ Whaaah！？」</t>
+          <t>Hah, huff！ Whaaah！？</t>
         </is>
       </c>
       <c r="C795" t="n">
@@ -12680,8 +12727,8 @@
       </c>
       <c r="B796" s="1" t="inlineStr">
         <is>
-          <t>When I spread the grabbed butt cheeks left and right,
-a tiny hole showed itself, but it immediately
+          <t>When he spread the grabbed butt cheeks left and
+right, a tiny hole showed itself, but it immediately
 squeezed shut and hid away, embarrassed.</t>
         </is>
       </c>
@@ -12944,7 +12991,7 @@
       <c r="B813" s="1" t="inlineStr">
         <is>
           <t>Those slightly worried eyes, at the same time,
-somehow look like she's expecting something.</t>
+somehow look like they're expecting something.</t>
         </is>
       </c>
       <c r="C813" t="n">
@@ -13875,8 +13922,8 @@
       <c r="B873" s="1" t="inlineStr">
         <is>
           <t>Thinking it would be better to take my time getting
-her used to it, I scooped up her arousal with a
-finger and rubbed it into her butt.</t>
+him used to it, I scooped up my arousal with a finger
+and rubbed it into his butt.</t>
         </is>
       </c>
       <c r="C873" t="n">
@@ -13906,7 +13953,7 @@
       </c>
       <c r="B875" s="1" t="inlineStr">
         <is>
-          <t>「See, your asshole is getting softer and softer~」</t>
+          <t>See, your asshole is getting softer and softer~</t>
         </is>
       </c>
       <c r="C875" t="n">
@@ -14013,8 +14060,8 @@
       </c>
       <c r="B882" s="1" t="inlineStr">
         <is>
-          <t>...Maybe Nono-chan’s butt is way more compatible than
-I thought.</t>
+          <t>...Maybe Nono-chan and my butt are way more
+compatible than I thought.</t>
         </is>
       </c>
       <c r="C882" t="n">
@@ -14106,7 +14153,7 @@
       </c>
       <c r="B888" s="1" t="inlineStr">
         <is>
-          <t>「Y-yes…！ Ah, ugh！？」</t>
+          <t>Y-yes…！ Ah, ugh！？</t>
         </is>
       </c>
       <c r="C888" t="n">
@@ -14289,8 +14336,8 @@
       </c>
       <c r="B900" s="1" t="inlineStr">
         <is>
-          <t>I pulled my fingers away from the hole, then went
-back to kneading her butt with my hand.</t>
+          <t>She pulled her fingers away from the hole, then went
+back to kneading my butt with her hand.</t>
         </is>
       </c>
       <c r="C900" t="n">
@@ -14381,8 +14428,7 @@
       </c>
       <c r="B906" s="1" t="inlineStr">
         <is>
-          <t>Serious Nono-chan is dutifully worried about her
-butt.</t>
+          <t>Serious Nono-chan is dutifully worried about my butt.</t>
         </is>
       </c>
       <c r="C906" t="n">
@@ -15154,7 +15200,7 @@
       </c>
       <c r="B956" s="1" t="inlineStr">
         <is>
-          <t>「Unya！ Manko！ Even so... my ass！ Again！ Nngh！」</t>
+          <t>Unya！ Manko！ Even so... my ass！ Again！ Nngh！</t>
         </is>
       </c>
       <c r="C956" t="n">
@@ -15354,8 +15400,8 @@
       </c>
       <c r="B969" s="1" t="inlineStr">
         <is>
-          <t>「Auu, ha！ I might cum… ahhh！ The spot around my
-asshole feels so good… haaau！」</t>
+          <t>Auu, ha！ I might cum… ahhh！ The spot around my
+asshole feels so good… haaau！</t>
         </is>
       </c>
       <c r="C969" t="n">
@@ -15415,7 +15461,7 @@
       </c>
       <c r="B973" s="1" t="inlineStr">
         <is>
-          <t>「Do you feel the penis and a finger inside together？」</t>
+          <t>Do you feel the penis and a finger inside together？</t>
         </is>
       </c>
       <c r="C973" t="n">
@@ -15506,8 +15552,8 @@
       </c>
       <c r="B979" s="1" t="inlineStr">
         <is>
-          <t>「Just a little more！ Let's make you cum with your
-butt, okay！'」</t>
+          <t>Just a little more！ Let's make you cum with your
+butt, okay！」</t>
         </is>
       </c>
       <c r="C979" t="n">
@@ -15814,8 +15860,7 @@
       </c>
       <c r="B999" s="1" t="inlineStr">
         <is>
-          <t>「Hanyaaaah！ My ass—！ Haaauu, ah！ Aahhh！
-Aaaahhhhhh……！」</t>
+          <t>Hanyaaaah！ My ass—！ Haaauu, ah！ Aahhh！ Aaaahhhhhh……！</t>
         </is>
       </c>
       <c r="C999" t="n">
@@ -15847,7 +15892,7 @@
       <c r="B1001" s="1" t="inlineStr">
         <is>
           <t>With that sudden jolt, the thumb I’d been pressing
-against her anus squelched right into the tiny hole.</t>
+against my anus squelched right into the tiny hole.</t>
         </is>
       </c>
       <c r="C1001" t="n">
@@ -16265,7 +16310,7 @@
       </c>
       <c r="B1028" s="1" t="inlineStr">
         <is>
-          <t>「Nn... fu, fuu... fuu... fuu...！」</t>
+          <t>Nn... fu, fuu... fuu... fuu...！</t>
         </is>
       </c>
       <c r="C1028" t="n">
@@ -16357,7 +16402,7 @@
       </c>
       <c r="B1034" s="1" t="inlineStr">
         <is>
-          <t>She’s probably looking forward to getting to savor
+          <t>They’re probably looking forward to getting to savor
 the afterglow of happiness from now on.</t>
         </is>
       </c>
@@ -16725,8 +16770,8 @@
       </c>
       <c r="B1058" s="1" t="inlineStr">
         <is>
-          <t>I put bloomers on her, and then I also lift up the
-pants that had slipped down to my ankles…！</t>
+          <t>I put bloomers on them, and then I also lift up the
+pants that had slipped down to their ankles…！</t>
         </is>
       </c>
       <c r="C1058" t="n">
@@ -16970,7 +17015,7 @@
       </c>
       <c r="B1074" s="1" t="inlineStr">
         <is>
-          <t>I hurriedly try to cover it up, but there's no
+          <t>He hurriedly tries to cover it up, but there's no
 reaction from anyone.</t>
         </is>
       </c>
@@ -17124,7 +17169,7 @@
       </c>
       <c r="B1084" s="1" t="inlineStr">
         <is>
-          <t>「Oh... so you two were eating by yourselves？」</t>
+          <t>Oh... so you two were eating by yourselves？</t>
         </is>
       </c>
       <c r="C1084" t="n">
